--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.0481</v>
+        <v>16.74817</v>
       </c>
       <c r="D2" t="n">
-        <v>16.34555</v>
+        <v>16.25932</v>
       </c>
       <c r="E2" t="n">
-        <v>16.07204</v>
+        <v>16.43164</v>
       </c>
       <c r="F2" t="n">
-        <v>42.04659</v>
+        <v>42.20994</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0503</v>
+        <v>0.04982</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82918</v>
+        <v>1.81356</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.55532</v>
+        <v>16.47</v>
       </c>
       <c r="D3" t="n">
-        <v>16.6876</v>
+        <v>16.23968</v>
       </c>
       <c r="E3" t="n">
-        <v>16.38068</v>
+        <v>16.42594</v>
       </c>
       <c r="F3" t="n">
-        <v>42.3566</v>
+        <v>41.84439</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04976</v>
+        <v>0.05119</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81557</v>
+        <v>1.78821</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.83447</v>
+        <v>16.84573</v>
       </c>
       <c r="D4" t="n">
-        <v>16.39265</v>
+        <v>16.50901</v>
       </c>
       <c r="E4" t="n">
-        <v>16.34077</v>
+        <v>16.55327</v>
       </c>
       <c r="F4" t="n">
-        <v>42.07275</v>
+        <v>42.36563</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04989</v>
+        <v>0.05011</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82596</v>
+        <v>1.84145</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.64857</v>
+        <v>16.6063</v>
       </c>
       <c r="D6" t="n">
-        <v>15.73336</v>
+        <v>15.95755</v>
       </c>
       <c r="E6" t="n">
-        <v>16.44512</v>
+        <v>16.1872</v>
       </c>
       <c r="F6" t="n">
-        <v>21.91352</v>
+        <v>21.11274</v>
       </c>
       <c r="G6" t="n">
-        <v>33.19787</v>
+        <v>33.52775</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.67164</v>
+        <v>16.39599</v>
       </c>
       <c r="D7" t="n">
-        <v>15.97789</v>
+        <v>16.04383</v>
       </c>
       <c r="E7" t="n">
-        <v>16.46445</v>
+        <v>16.12546</v>
       </c>
       <c r="F7" t="n">
-        <v>21.70585</v>
+        <v>21.33787</v>
       </c>
       <c r="G7" t="n">
-        <v>33.9631</v>
+        <v>34.42284</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.34343</v>
+        <v>16.49274</v>
       </c>
       <c r="D8" t="n">
-        <v>15.5859</v>
+        <v>15.88618</v>
       </c>
       <c r="E8" t="n">
-        <v>16.56011</v>
+        <v>16.14287</v>
       </c>
       <c r="F8" t="n">
-        <v>21.37684</v>
+        <v>21.77436</v>
       </c>
       <c r="G8" t="n">
-        <v>33.22698</v>
+        <v>34.34037</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.59309</v>
+        <v>0.5938099999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>1.09909</v>
+        <v>1.10521</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.59211</v>
+        <v>0.60987</v>
       </c>
       <c r="D11" t="n">
-        <v>1.08613</v>
+        <v>1.11031</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6035199999999999</v>
+        <v>0.59645</v>
       </c>
       <c r="D12" t="n">
-        <v>1.12095</v>
+        <v>1.09582</v>
       </c>
     </row>
   </sheetData>
